--- a/CodeSystem-view-type-codesystem.xlsx
+++ b/CodeSystem-view-type-codesystem.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>UI Component Types</t>
+    <t>UI Component Types (example)</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T08:14:58+00:00</t>
+    <t>2026-06-09T19:54:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,9 +81,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Formal codes for identifying UI component factories in the KMP ViewRegistry.
-Each code maps to a registered ComponentRenderer that knows how to render
-a specific FHIR-derived view state on screen.</t>
+    <t>**Example** vocabulary of view types. Each code names a kind of UI component used to render a piece of
+FHIR-derived data; a ViewConfig binds to one of these codes to select its component. View types are
+implementer-defined — a player provides its own CodeSystem rather than reusing these codes. The mapping
+from a code to a concrete renderer is the player's own implementation detail.</t>
   </si>
   <si>
     <t>Purpose</t>
